--- a/data/raw/北证A股近期走势.xlsx
+++ b/data/raw/北证A股近期走势.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuanhm\Documents\GitHub\bse_dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676D5784-D20D-4715-A3AC-E8570FF2C75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC89066A-E324-41F7-8FF7-920714E343D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
